--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484584_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484584_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>G. BORREGA BERTOLIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.781</v>
+        <v>1.403</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6393</v>
+        <v>1.0143</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1417</v>
+        <v>0.3888</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8149</v>
+        <v>3.1464</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.9367</v>
+        <v>0.5114</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1218</v>
+        <v>2.635</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1292</v>
+        <v>5.1463</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2936</v>
+        <v>1.8699</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4228</v>
+        <v>3.2764</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6857</v>
+        <v>-1.9999</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2303</v>
+        <v>-1.3585</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5446</v>
+        <v>-0.6413</v>
       </c>
       <c r="P2" t="n">
-        <v>0.733</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9163</v>
+        <v>-4.7647</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6493</v>
+        <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>2.568</v>
+        <v>0.3154</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7292999999999999</v>
+        <v>-0.3228</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8387</v>
+        <v>0.6382</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.7052</v>
+        <v>0.5068</v>
       </c>
       <c r="W2" t="n">
         <v>0.9554</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.6606</v>
+        <v>-0.4486</v>
       </c>
     </row>
     <row r="3">
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. BORREGA BERTOLIN</t>
+          <t>G. PARDO GALLENT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4545</v>
+        <v>0.0721</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4373</v>
+        <v>-0.0334</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0172</v>
+        <v>0.1055</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1464</v>
+        <v>-0.1387</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5114</v>
+        <v>0.1499</v>
       </c>
       <c r="I4" t="n">
-        <v>2.635</v>
+        <v>-0.2885</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1463</v>
+        <v>0.0217</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8699</v>
+        <v>0.0217</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2764</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9999</v>
+        <v>-0.1603</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3585</v>
+        <v>0.1282</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6413</v>
+        <v>-0.2885</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.5656</v>
+        <v>0.1833</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.7647</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1991</v>
+        <v>0.1833</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6331</v>
+        <v>0.0275</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.0551</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2666</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5068</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4486</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. PARDO GALLENT</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0226</v>
+        <v>0.0169</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0334</v>
+        <v>0.1724</v>
       </c>
       <c r="F5" t="n">
-        <v>0.056</v>
+        <v>-0.1555</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1387</v>
+        <v>-0.8149</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1499</v>
+        <v>-0.9367</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2885</v>
+        <v>0.1218</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0217</v>
+        <v>-0.1292</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0217</v>
+        <v>0.2936</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.4228</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1603</v>
+        <v>-0.6857</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1282</v>
+        <v>-1.2303</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2885</v>
+        <v>0.5446</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1833</v>
+        <v>0.733</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1833</v>
+        <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.022</v>
+        <v>1.8039</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0551</v>
+        <v>0.2625</v>
       </c>
       <c r="U5" t="n">
-        <v>0.033</v>
+        <v>1.5414</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.7052</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.6606</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3477</v>
+        <v>-0.2572</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7426</v>
+        <v>-0.4952</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3949</v>
+        <v>0.238</v>
       </c>
       <c r="G6" t="n">
         <v>-3.1411</v>
@@ -922,13 +922,13 @@
         <v>1.4661</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9855</v>
+        <v>1.076</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2405</v>
+        <v>0.0068</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2261</v>
+        <v>1.0692</v>
       </c>
       <c r="V6" t="n">
         <v>1.4414</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8642</v>
+        <v>-0.8062</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0268</v>
+        <v>-1.0679</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1627</v>
+        <v>0.2618</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8925999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>0.5498</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0834</v>
+        <v>0.1414</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0905</v>
+        <v>0.0494</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0071</v>
+        <v>0.092</v>
       </c>
       <c r="V7" t="n">
         <v>0.3115</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DIAGO ROS</t>
+          <t>I. ALONSO QUINZA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2268</v>
+        <v>-1.3934</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.1435</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3261</v>
+        <v>-1.2499</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6334</v>
+        <v>0.2781</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1524</v>
+        <v>0.0217</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.481</v>
+        <v>0.2564</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1084</v>
+        <v>0.0217</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1084</v>
+        <v>0.0217</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7418</v>
+        <v>0.2564</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2608</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.481</v>
+        <v>0.2564</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2234</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0905</v>
+        <v>-0.1652</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1329</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. ALONSO QUINZA</t>
+          <t>A. DIAGO ROS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.443</v>
+        <v>-1.5648</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1435</v>
+        <v>-1.1891</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2995</v>
+        <v>-0.3757</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2781</v>
+        <v>-1.6334</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0217</v>
+        <v>-1.1524</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2564</v>
+        <v>-0.481</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0217</v>
+        <v>0.1084</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0217</v>
+        <v>0.1084</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2564</v>
+        <v>-1.7418</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-1.2608</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2564</v>
+        <v>-0.481</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1321</v>
+        <v>-0.1146</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1652</v>
+        <v>-0.198</v>
       </c>
       <c r="U9" t="n">
-        <v>0.033</v>
+        <v>0.0833</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SAEZ GONZALEZ</t>
+          <t>P. FERRI BARCENAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3851</v>
+        <v>-1.6403</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5071</v>
+        <v>-3.4675</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1221</v>
+        <v>1.8272</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8602</v>
+        <v>-3.5185</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9309</v>
+        <v>-1.1211</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0706</v>
+        <v>-2.3974</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0388</v>
+        <v>-2.4391</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5327</v>
+        <v>0.6312</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5062</v>
+        <v>-3.0703</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8214</v>
+        <v>-1.0795</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3982</v>
+        <v>-1.7523</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5768</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.733</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9163</v>
+        <v>-2.0158</v>
       </c>
       <c r="R10" t="n">
         <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4578</v>
+        <v>0.471</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.552</v>
+        <v>-0.612</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0098</v>
+        <v>1.0829</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.7156</v>
+        <v>1.7738</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.5993</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7156</v>
+        <v>0.1744</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X. CORTINA CAMPOS</t>
+          <t>R. TORREGROSA ROCA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4235</v>
+        <v>-2.2605</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.811</v>
+        <v>-1.9345</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6125</v>
+        <v>-0.326</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.6113</v>
+        <v>-4.0498</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.066</v>
+        <v>-2.1038</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5453</v>
+        <v>-1.946</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2115</v>
+        <v>-1.6988</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.0128</v>
+        <v>-1.0995</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1987</v>
+        <v>-0.5994</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.3999</v>
+        <v>-2.351</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0532</v>
+        <v>-1.0044</v>
       </c>
       <c r="O11" t="n">
         <v>-1.3466</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5098</v>
+        <v>0.4619</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5</v>
+        <v>-0.2356</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0098</v>
+        <v>0.6976</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3219</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. TORREGROSA ROCA</t>
+          <t>J. SAEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6532</v>
+        <v>-2.5366</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5253</v>
+        <v>-2.411</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1279</v>
+        <v>-0.1257</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.0498</v>
+        <v>-1.8602</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1038</v>
+        <v>-1.9309</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.946</v>
+        <v>0.0706</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6988</v>
+        <v>-1.0388</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0995</v>
+        <v>-0.5327</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5994</v>
+        <v>-0.5062</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.351</v>
+        <v>-0.8214</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0044</v>
+        <v>-1.3982</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3466</v>
+        <v>0.5768</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6493</v>
+        <v>0.733</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R12" t="n">
         <v>1.6493</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0692</v>
+        <v>0.3062</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8265</v>
+        <v>-0.4559</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8958</v>
+        <v>0.762</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3219</v>
+        <v>-1.7156</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3219</v>
+        <v>-1.7156</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7018</v>
+        <v>-2.7207</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.0964</v>
+        <v>-3.2887</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3946</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-1.1018</v>
@@ -1468,13 +1468,13 @@
         <v>1.2828</v>
       </c>
       <c r="S13" t="n">
-        <v>0.188</v>
+        <v>0.1691</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0536</v>
+        <v>-0.1387</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1345</v>
+        <v>0.3079</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3219</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. FERRI BARCENAS</t>
+          <t>X. CORTINA CAMPOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.919</v>
+        <v>-3.4265</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.2507</v>
+        <v>-2.5663</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3317</v>
+        <v>-0.8602</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.5185</v>
+        <v>-4.6113</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1211</v>
+        <v>-2.066</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.3974</v>
+        <v>-2.5453</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.4391</v>
+        <v>-2.2115</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6312</v>
+        <v>-1.0128</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.0703</v>
+        <v>-1.1987</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0795</v>
+        <v>-2.3999</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7523</v>
+        <v>-1.0532</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6729000000000001</v>
+        <v>-1.3466</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0158</v>
+        <v>-1.0995</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8077</v>
+        <v>1.5068</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3951</v>
+        <v>0.7447</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5875</v>
+        <v>0.762</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7738</v>
+        <v>-0.3219</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5993</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1744</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-15.0811</v>
+        <v>-14.4891</v>
       </c>
       <c r="E15" t="n">
-        <v>-15.3358</v>
+        <v>-14.7853</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2549000000000001</v>
+        <v>0.2962999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-17.7127</v>
@@ -1615,7 +1615,7 @@
         <v>-1.7654</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9162999999999997</v>
+        <v>-0.9162999999999998</v>
       </c>
       <c r="Q15" t="n">
         <v>-15.5768</v>
@@ -1624,13 +1624,13 @@
         <v>14.6606</v>
       </c>
       <c r="S15" t="n">
-        <v>5.4902</v>
+        <v>6.082000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.6702</v>
+        <v>-1.1199</v>
       </c>
       <c r="U15" t="n">
-        <v>7.160600000000001</v>
+        <v>7.201700000000001</v>
       </c>
       <c r="V15" t="n">
         <v>-1.9419</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.5711</v>
+        <v>6.7707</v>
       </c>
       <c r="E16" t="n">
-        <v>5.0318</v>
+        <v>4.7434</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5392</v>
+        <v>2.0273</v>
       </c>
       <c r="G16" t="n">
         <v>5.9589</v>
@@ -1702,13 +1702,13 @@
         <v>2.3823</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6206</v>
+        <v>-0.421</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6252</v>
+        <v>-0.9136</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0046</v>
+        <v>0.4926</v>
       </c>
       <c r="V16" t="n">
         <v>1.5993</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8598</v>
+        <v>3.969</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8757</v>
+        <v>0.9719</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9841</v>
+        <v>2.9971</v>
       </c>
       <c r="G17" t="n">
         <v>2.2704</v>
@@ -1780,13 +1780,13 @@
         <v>2.1991</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3556</v>
+        <v>-0.2464</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2111</v>
+        <v>-1.115</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8555</v>
+        <v>0.8686</v>
       </c>
       <c r="V17" t="n">
         <v>1.5785</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1115</v>
+        <v>3.123</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3233</v>
+        <v>-1.131</v>
       </c>
       <c r="F18" t="n">
-        <v>4.4349</v>
+        <v>4.254</v>
       </c>
       <c r="G18" t="n">
         <v>3.4241</v>
@@ -1858,13 +1858,13 @@
         <v>2.5656</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4225</v>
+        <v>-0.411</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3763</v>
+        <v>-1.184</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9538</v>
+        <v>0.773</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6231</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.7236</v>
+        <v>2.6668</v>
       </c>
       <c r="E19" t="n">
-        <v>0.161</v>
+        <v>-0.1275</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5626</v>
+        <v>2.7943</v>
       </c>
       <c r="G19" t="n">
         <v>1.9959</v>
@@ -1936,13 +1936,13 @@
         <v>1.2828</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0393</v>
+        <v>-0.0175</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1297</v>
+        <v>-0.4182</v>
       </c>
       <c r="U19" t="n">
-        <v>0.169</v>
+        <v>0.4006</v>
       </c>
       <c r="V19" t="n">
         <v>0.3219</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5591</v>
+        <v>2.2322</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2918</v>
+        <v>0.5802</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2673</v>
+        <v>1.6519</v>
       </c>
       <c r="G20" t="n">
         <v>0.723</v>
@@ -2014,13 +2014,13 @@
         <v>2.1991</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0618</v>
+        <v>-0.3888</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2111</v>
+        <v>-0.9227</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1493</v>
+        <v>0.5339</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3011</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4146</v>
+        <v>0.6842</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1188</v>
+        <v>0.2149</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2958</v>
+        <v>0.4693</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0698</v>
@@ -2170,13 +2170,13 @@
         <v>0.5498</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4161</v>
+        <v>-0.1465</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2753</v>
+        <v>-0.1791</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1408</v>
+        <v>0.0326</v>
       </c>
       <c r="V22" t="n">
         <v>1.267</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. IGUAL BAU</t>
+          <t>C. WHITSON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0292</v>
+        <v>0.4463</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0283</v>
+        <v>-0.2227</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0009</v>
+        <v>0.669</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0512</v>
+        <v>0.3116</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1282</v>
+        <v>1.5039</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.077</v>
+        <v>-1.1923</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0833</v>
+        <v>-0.2619</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0833</v>
+        <v>-1.0638</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0321</v>
+        <v>0.5735</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1282</v>
+        <v>0.702</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1603</v>
+        <v>-0.1285</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.022</v>
+        <v>-0.5537</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0551</v>
+        <v>-0.6335</v>
       </c>
       <c r="U23" t="n">
-        <v>0.033</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. HOLGADO CUELLAR</t>
+          <t>D. IGUAL BAU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.0459</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3891</v>
+        <v>0.0283</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3432</v>
+        <v>0.0505</v>
       </c>
       <c r="G24" t="n">
-        <v>2.0066</v>
+        <v>0.0512</v>
       </c>
       <c r="H24" t="n">
-        <v>3.8304</v>
+        <v>0.1282</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8238</v>
+        <v>-0.077</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9187</v>
+        <v>0.0833</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7743</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.8556</v>
+        <v>0.0833</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0879</v>
+        <v>-0.0321</v>
       </c>
       <c r="N24" t="n">
-        <v>1.0561</v>
+        <v>0.1282</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0318</v>
+        <v>-0.1603</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.9321</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2461</v>
+        <v>0.0275</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0355</v>
+        <v>-0.0551</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2107</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C. WHITSON</t>
+          <t>R. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5227000000000001</v>
+        <v>-0.1537</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.415</v>
+        <v>-2.7737</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1076</v>
+        <v>2.62</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3116</v>
+        <v>2.0066</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5039</v>
+        <v>3.8304</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.1923</v>
+        <v>-1.8238</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.2619</v>
+        <v>0.9187</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8018999999999999</v>
+        <v>2.7743</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.0638</v>
+        <v>-1.8556</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5735</v>
+        <v>1.0879</v>
       </c>
       <c r="N25" t="n">
-        <v>0.702</v>
+        <v>1.0561</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1285</v>
+        <v>0.0318</v>
       </c>
       <c r="P25" t="n">
-        <v>0.3665</v>
+        <v>-2.9321</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2828</v>
+        <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5227</v>
+        <v>0.1384</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8258</v>
+        <v>-0.3492</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6969</v>
+        <v>0.4875</v>
       </c>
       <c r="V25" t="n">
+        <v>0.6335</v>
+      </c>
+      <c r="W25" t="n">
         <v>0.3219</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.5889</v>
-      </c>
       <c r="X25" t="n">
-        <v>-1.267</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. NEBOT GARCIA</t>
+          <t>C. FUSTER ROYO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7865</v>
+        <v>-0.3799</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.2342</v>
+        <v>-1.6366</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4477</v>
+        <v>1.2567</v>
       </c>
       <c r="G26" t="n">
-        <v>1.061</v>
+        <v>-1.258</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2564</v>
+        <v>-1.7483</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8045</v>
+        <v>0.4902</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0674</v>
+        <v>-0.7419</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.641</v>
+        <v>-0.7835</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7085</v>
+        <v>0.0417</v>
       </c>
       <c r="M26" t="n">
-        <v>0.9935</v>
+        <v>-0.5161</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8974</v>
+        <v>-0.9647</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0961</v>
+        <v>0.4486</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.3665</v>
+        <v>1.8326</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5498</v>
+        <v>1.8326</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.214</v>
+        <v>-0.6325</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3854</v>
+        <v>-0.8948</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1714</v>
+        <v>0.2622</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C. FUSTER ROYO</t>
+          <t>M. NEBOT GARCIA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8272</v>
+        <v>-0.8608</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.7328</v>
+        <v>-1.2342</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9056</v>
+        <v>0.3734</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.258</v>
+        <v>1.061</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.7483</v>
+        <v>0.2564</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4902</v>
+        <v>0.8045</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.7419</v>
+        <v>0.0674</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.7835</v>
+        <v>-0.641</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0417</v>
+        <v>0.7085</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.5161</v>
+        <v>0.9935</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.9647</v>
+        <v>0.8974</v>
       </c>
       <c r="O27" t="n">
-        <v>0.4486</v>
+        <v>0.0961</v>
       </c>
       <c r="P27" t="n">
-        <v>1.8326</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R27" t="n">
-        <v>1.8326</v>
+        <v>0.5498</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.0799</v>
+        <v>-0.2883</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9909</v>
+        <v>-0.3854</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.08890000000000001</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.2811</v>
+        <v>-2.2068</v>
       </c>
       <c r="E28" t="n">
         <v>-0.9429999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.3381</v>
+        <v>-1.2638</v>
       </c>
       <c r="G28" t="n">
         <v>-0.0373</v>
@@ -2638,13 +2638,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.0606</v>
+        <v>0.0138</v>
       </c>
       <c r="T28" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0495</v>
+        <v>0.1239</v>
       </c>
       <c r="V28" t="n">
         <v>-1.267</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>15.0808</v>
+        <v>17.645</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2547000000000003</v>
+        <v>-0.2546999999999991</v>
       </c>
       <c r="F29" t="n">
-        <v>15.3356</v>
+        <v>17.8997</v>
       </c>
       <c r="G29" t="n">
         <v>17.7129</v>
@@ -2686,7 +2686,7 @@
         <v>13.7058</v>
       </c>
       <c r="I29" t="n">
-        <v>4.006699999999999</v>
+        <v>4.0067</v>
       </c>
       <c r="J29" t="n">
         <v>13.5797</v>
@@ -2704,10 +2704,10 @@
         <v>1.8914</v>
       </c>
       <c r="O29" t="n">
-        <v>2.241400000000001</v>
+        <v>2.2414</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9163</v>
+        <v>0.9162999999999996</v>
       </c>
       <c r="Q29" t="n">
         <v>-14.6607</v>
@@ -2716,22 +2716,22 @@
         <v>15.5769</v>
       </c>
       <c r="S29" t="n">
-        <v>-5.4904</v>
+        <v>-2.926</v>
       </c>
       <c r="T29" t="n">
-        <v>-7.1605</v>
+        <v>-7.160699999999999</v>
       </c>
       <c r="U29" t="n">
-        <v>1.6702</v>
+        <v>4.234299999999999</v>
       </c>
       <c r="V29" t="n">
-        <v>1.942000000000001</v>
+        <v>1.941999999999999</v>
       </c>
       <c r="W29" t="n">
-        <v>7.9862</v>
+        <v>7.986200000000001</v>
       </c>
       <c r="X29" t="n">
-        <v>-6.0442</v>
+        <v>-6.044199999999998</v>
       </c>
     </row>
   </sheetData>
